--- a/Collections/EURO/Malta/#EURO#Malta#Regular#[2008-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Malta/#EURO#Malta#Regular#[2008-present]#circulation_quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Malta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC6A150-0CA0-4208-820D-DE5043BF3FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0810C5F-3FDA-41C7-8ED8-84D213ED2E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cent" sheetId="4" r:id="rId1"/>
@@ -46,6 +46,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -644,7 +647,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="96">
   <si>
     <t>-</t>
   </si>
@@ -865,9 +868,6 @@
     <t>3.111.000</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>2.001.000</t>
   </si>
   <si>
@@ -905,6 +905,36 @@
   </si>
   <si>
     <t>Subtype_2#Map_of_Europe</t>
+  </si>
+  <si>
+    <t>4.010.000</t>
+  </si>
+  <si>
+    <t>7.000</t>
+  </si>
+  <si>
+    <t>4.910.000</t>
+  </si>
+  <si>
+    <t>4.611.000</t>
+  </si>
+  <si>
+    <t>3.610.000</t>
+  </si>
+  <si>
+    <t>7.011.000</t>
+  </si>
+  <si>
+    <t>1.110.000</t>
+  </si>
+  <si>
+    <t>2.300.000</t>
+  </si>
+  <si>
+    <t>1.810.000</t>
+  </si>
+  <si>
+    <t>510.000</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1308,1391 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="127">
+  <dxfs count="176">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1287,998 +2701,6 @@
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2311,9 +2733,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="175"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="174" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="173"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2582,7 +3004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -2615,13 +3037,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="24"/>
       <c r="B2" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>29</v>
@@ -2922,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>0</v>
@@ -2952,7 +3374,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>0</v>
@@ -2982,7 +3404,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>0</v>
@@ -3042,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>0</v>
@@ -3066,15 +3488,15 @@
         <v>54</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="18">
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
@@ -3096,7 +3518,7 @@
         <v>54</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>60</v>
@@ -3112,6 +3534,66 @@
       </c>
       <c r="I18" s="3" t="str">
         <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" ref="I19:I20" si="2">IF(OR(AND(G19&gt;1,G19&lt;&gt;"-"),AND(H19&gt;1,H19&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3125,12 +3607,12 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G4:G7 G9:G10">
-    <cfRule type="containsText" dxfId="126" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="172" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G7 G9:G10">
-    <cfRule type="colorScale" priority="40">
+    <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3142,12 +3624,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H10">
-    <cfRule type="containsText" dxfId="125" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="171" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H10">
-    <cfRule type="colorScale" priority="38">
+    <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3159,11 +3641,130 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11">
-    <cfRule type="containsText" dxfId="124" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="170" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="169" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G16">
+    <cfRule type="containsText" dxfId="168" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G16">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="containsText" dxfId="167" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="containsText" dxfId="166" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="165" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="containsText" dxfId="164" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="containsText" dxfId="163" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3175,12 +3776,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="123" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
+  <conditionalFormatting sqref="H13">
+    <cfRule type="containsText" dxfId="162" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3192,12 +3793,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G12:G16">
-    <cfRule type="containsText" dxfId="122" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12:G16">
+  <conditionalFormatting sqref="H14">
+    <cfRule type="containsText" dxfId="161" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3209,12 +3810,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
-    <cfRule type="containsText" dxfId="121" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
+  <conditionalFormatting sqref="H16">
+    <cfRule type="containsText" dxfId="160" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3226,46 +3827,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
-    <cfRule type="containsText" dxfId="120" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="119" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="containsText" dxfId="118" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
+  <conditionalFormatting sqref="G18">
+    <cfRule type="containsText" dxfId="159" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3277,12 +3844,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="117" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
+  <conditionalFormatting sqref="H17:H18">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3294,12 +3856,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="116" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
+  <conditionalFormatting sqref="H17:H18">
+    <cfRule type="containsText" dxfId="158" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17">
+    <cfRule type="containsText" dxfId="157" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3311,12 +3878,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
-    <cfRule type="containsText" dxfId="115" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
+  <conditionalFormatting sqref="G19">
+    <cfRule type="containsText" dxfId="47" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3328,12 +3895,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="containsText" dxfId="114" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
+  <conditionalFormatting sqref="H19">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3345,12 +3907,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
-    <cfRule type="containsText" dxfId="113" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="46" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="45" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3362,7 +3929,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H18">
+  <conditionalFormatting sqref="H20">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3374,9 +3941,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H18">
-    <cfRule type="containsText" dxfId="112" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="44" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3387,7 +3954,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -3420,13 +3987,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="24"/>
       <c r="B2" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>29</v>
@@ -3757,7 +4324,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>0</v>
@@ -3817,7 +4384,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>0</v>
@@ -3826,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="3" t="str">
-        <f t="shared" ref="I15:I18" si="1">IF(OR(AND(G15&gt;1,G15&lt;&gt;"-"),AND(H15&gt;1,H15&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I15:I20" si="1">IF(OR(AND(G15&gt;1,G15&lt;&gt;"-"),AND(H15&gt;1,H15&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -3847,7 +4414,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>0</v>
@@ -3871,15 +4438,15 @@
         <v>54</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="18">
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
@@ -3901,7 +4468,7 @@
         <v>54</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>60</v>
@@ -3916,6 +4483,66 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3930,6 +4557,193 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G12:G16">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12 H14">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H10">
+    <cfRule type="containsText" dxfId="156" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H10">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="155" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="containsText" dxfId="154" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11">
+    <cfRule type="containsText" dxfId="153" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="152" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G16">
+    <cfRule type="containsText" dxfId="151" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12 H14">
+    <cfRule type="containsText" dxfId="150" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G10">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G7 G9">
+    <cfRule type="containsText" dxfId="149" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G7 G9">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="containsText" dxfId="148" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G10">
+    <cfRule type="containsText" dxfId="147" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G10))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
+    <cfRule type="containsText" dxfId="146" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17:H18">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3941,7 +4755,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12 H14">
+  <conditionalFormatting sqref="H17:H18">
+    <cfRule type="containsText" dxfId="145" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="containsText" dxfId="144" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3953,102 +4777,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H10">
-    <cfRule type="containsText" dxfId="111" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H10">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="110" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="containsText" dxfId="109" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
-    <cfRule type="containsText" dxfId="108" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="107" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12:G16">
-    <cfRule type="containsText" dxfId="106" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12 H14">
-    <cfRule type="containsText" dxfId="105" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
+  <conditionalFormatting sqref="H15">
+    <cfRule type="containsText" dxfId="143" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4060,7 +4794,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G10">
+  <conditionalFormatting sqref="H13">
+    <cfRule type="containsText" dxfId="142" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4072,39 +4811,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G7 G9">
-    <cfRule type="containsText" dxfId="104" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G7 G9">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
-    <cfRule type="containsText" dxfId="103" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G10">
-    <cfRule type="containsText" dxfId="102" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G10))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
-    <cfRule type="containsText" dxfId="101" priority="9" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G17">
+    <cfRule type="containsText" dxfId="43" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G17))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
+  <conditionalFormatting sqref="G17">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4116,7 +4828,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H18">
+  <conditionalFormatting sqref="G19">
+    <cfRule type="containsText" dxfId="42" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4128,17 +4845,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H18">
-    <cfRule type="containsText" dxfId="100" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="containsText" dxfId="99" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
+  <conditionalFormatting sqref="H19">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4150,12 +4857,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
-    <cfRule type="containsText" dxfId="98" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="41" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="40" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4167,12 +4879,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="97" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
+  <conditionalFormatting sqref="H20">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4182,6 +4889,11 @@
         <color rgb="FFD1E0B2"/>
         <color rgb="FF00B050"/>
       </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="39" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4192,7 +4904,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -4225,13 +4937,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="24"/>
       <c r="B2" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>29</v>
@@ -4532,7 +5244,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>0</v>
@@ -4592,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>0</v>
@@ -4622,7 +5334,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>0</v>
@@ -4631,7 +5343,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="3" t="str">
-        <f t="shared" ref="I15:I18" si="1">IF(OR(AND(G15&gt;1,G15&lt;&gt;"-"),AND(H15&gt;1,H15&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I15:I20" si="1">IF(OR(AND(G15&gt;1,G15&lt;&gt;"-"),AND(H15&gt;1,H15&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -4652,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>0</v>
@@ -4676,15 +5388,15 @@
         <v>54</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>90</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="18">
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
@@ -4706,21 +5418,81 @@
         <v>54</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E18" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3" t="str">
+      <c r="F19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4734,11 +5506,96 @@
     <mergeCell ref="G1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="96" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="141" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="containsText" dxfId="140" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11">
+    <cfRule type="containsText" dxfId="139" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="138" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G14">
+    <cfRule type="containsText" dxfId="137" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G14">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="containsText" dxfId="136" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4750,12 +5607,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="containsText" dxfId="95" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
+  <conditionalFormatting sqref="G8">
+    <cfRule type="containsText" dxfId="135" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4767,12 +5624,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
-    <cfRule type="containsText" dxfId="94" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
+  <conditionalFormatting sqref="G10">
+    <cfRule type="containsText" dxfId="134" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G10))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G10">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4784,12 +5641,46 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="93" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
+  <conditionalFormatting sqref="G4:G7 G9">
+    <cfRule type="containsText" dxfId="133" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G7 G9">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H10">
+    <cfRule type="containsText" dxfId="132" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H10">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="containsText" dxfId="131" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4801,12 +5692,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G12:G14">
-    <cfRule type="containsText" dxfId="92" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12:G14">
+  <conditionalFormatting sqref="H14">
+    <cfRule type="containsText" dxfId="130" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4818,12 +5709,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="91" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
+  <conditionalFormatting sqref="G15">
+    <cfRule type="containsText" dxfId="129" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4835,12 +5726,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
-    <cfRule type="containsText" dxfId="90" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
+  <conditionalFormatting sqref="H15">
+    <cfRule type="containsText" dxfId="128" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4852,12 +5743,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G10">
-    <cfRule type="containsText" dxfId="89" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G10))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G10">
+  <conditionalFormatting sqref="G16">
+    <cfRule type="containsText" dxfId="127" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G16">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4869,46 +5760,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G7 G9">
-    <cfRule type="containsText" dxfId="88" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G7 G9">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H10">
-    <cfRule type="containsText" dxfId="87" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H10">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="86" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
+  <conditionalFormatting sqref="H16">
+    <cfRule type="containsText" dxfId="126" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4920,12 +5777,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
-    <cfRule type="containsText" dxfId="85" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
+  <conditionalFormatting sqref="G18">
+    <cfRule type="containsText" dxfId="125" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4937,12 +5794,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G15">
-    <cfRule type="containsText" dxfId="84" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G15">
+  <conditionalFormatting sqref="H17:H18">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4954,12 +5806,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
-    <cfRule type="containsText" dxfId="83" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
+  <conditionalFormatting sqref="H17:H18">
+    <cfRule type="containsText" dxfId="124" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17">
+    <cfRule type="containsText" dxfId="37" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4971,12 +5828,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16">
-    <cfRule type="containsText" dxfId="82" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G16">
+  <conditionalFormatting sqref="G19">
+    <cfRule type="containsText" dxfId="36" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4988,12 +5845,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="containsText" dxfId="81" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
+  <conditionalFormatting sqref="H19">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5005,12 +5857,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
-    <cfRule type="containsText" dxfId="80" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="35" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="34" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5022,7 +5879,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H18">
+  <conditionalFormatting sqref="H20">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5034,9 +5891,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H18">
-    <cfRule type="containsText" dxfId="79" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5047,7 +5904,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -5080,13 +5937,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="32"/>
       <c r="B2" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>29</v>
@@ -5488,7 +6345,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="3" t="str">
-        <f t="shared" ref="I15:I18" si="1">IF(OR(AND(G15&gt;1,G15&lt;&gt;"-"),AND(H15&gt;1,H15&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I15:I20" si="1">IF(OR(AND(G15&gt;1,G15&lt;&gt;"-"),AND(H15&gt;1,H15&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -5535,13 +6392,13 @@
       <c r="D17" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="19" t="s">
-        <v>60</v>
+      <c r="E17" s="10" t="s">
+        <v>92</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="18">
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
@@ -5565,19 +6422,79 @@
       <c r="D18" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="18">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3" t="str">
+      <c r="F19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -5591,6 +6508,227 @@
     <mergeCell ref="G1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="H13">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G14">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H10">
+    <cfRule type="containsText" dxfId="123" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H10">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="122" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="containsText" dxfId="121" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11">
+    <cfRule type="containsText" dxfId="120" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="119" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G14">
+    <cfRule type="containsText" dxfId="118" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="containsText" dxfId="117" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="containsText" dxfId="116" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G7 G9:G10">
+    <cfRule type="containsText" dxfId="115" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G7 G9:G10">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="containsText" dxfId="114" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14">
+    <cfRule type="containsText" dxfId="113" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15">
+    <cfRule type="containsText" dxfId="112" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="containsText" dxfId="111" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G16">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5602,119 +6740,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12:G14">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H10">
-    <cfRule type="containsText" dxfId="78" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H10">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="77" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="containsText" dxfId="76" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
-    <cfRule type="containsText" dxfId="75" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="74" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12:G14">
-    <cfRule type="containsText" dxfId="73" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="72" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
-    <cfRule type="containsText" dxfId="71" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
+  <conditionalFormatting sqref="G16">
+    <cfRule type="containsText" dxfId="110" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="containsText" dxfId="109" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5726,46 +6762,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G7 G9:G10">
-    <cfRule type="containsText" dxfId="70" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G7 G9:G10">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="69" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
-    <cfRule type="containsText" dxfId="68" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
+  <conditionalFormatting sqref="H17:H18">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5777,7 +6774,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G15">
+  <conditionalFormatting sqref="H17:H18">
+    <cfRule type="containsText" dxfId="107" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17">
+    <cfRule type="containsText" dxfId="32" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5789,17 +6796,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G15">
-    <cfRule type="containsText" dxfId="67" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
-    <cfRule type="containsText" dxfId="66" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
+  <conditionalFormatting sqref="G18">
+    <cfRule type="containsText" dxfId="31" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5811,7 +6813,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16">
+  <conditionalFormatting sqref="G19">
+    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5823,17 +6830,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16">
-    <cfRule type="containsText" dxfId="65" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="containsText" dxfId="64" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
+  <conditionalFormatting sqref="H19">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5845,12 +6842,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
-    <cfRule type="containsText" dxfId="63" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="28" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5862,7 +6864,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H18">
+  <conditionalFormatting sqref="H20">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5874,9 +6876,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H18">
-    <cfRule type="containsText" dxfId="62" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="27" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5887,7 +6889,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -5920,13 +6922,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="32"/>
       <c r="B2" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>29</v>
@@ -6375,13 +7377,13 @@
       <c r="D17" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="19" t="s">
-        <v>60</v>
+      <c r="E17" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
@@ -6405,13 +7407,13 @@
       <c r="D18" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E18" s="19" t="s">
-        <v>60</v>
+      <c r="E18" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
@@ -6419,6 +7421,66 @@
       </c>
       <c r="I18" s="3" t="str">
         <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" ref="I19:I20" si="2">IF(OR(AND(G19&gt;1,G19&lt;&gt;"-"),AND(H19&gt;1,H19&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -6431,6 +7493,198 @@
     <mergeCell ref="G1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="H12:H13">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G14">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H10">
+    <cfRule type="containsText" dxfId="106" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H10">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="105" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="containsText" dxfId="104" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11">
+    <cfRule type="containsText" dxfId="103" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="102" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G14">
+    <cfRule type="containsText" dxfId="101" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12:H13">
+    <cfRule type="containsText" dxfId="100" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="containsText" dxfId="99" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G7 G9:G10">
+    <cfRule type="containsText" dxfId="98" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G7 G9:G10">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14">
+    <cfRule type="containsText" dxfId="97" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15">
+    <cfRule type="containsText" dxfId="96" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="containsText" dxfId="95" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6442,119 +7696,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12:G14">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H10">
-    <cfRule type="containsText" dxfId="61" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H10">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="60" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="containsText" dxfId="59" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
-    <cfRule type="containsText" dxfId="58" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="57" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12:G14">
-    <cfRule type="containsText" dxfId="56" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12:H13">
-    <cfRule type="containsText" dxfId="55" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
-    <cfRule type="containsText" dxfId="54" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
+  <conditionalFormatting sqref="G16">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6566,29 +7708,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G7 G9:G10">
-    <cfRule type="containsText" dxfId="53" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G7 G9:G10">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
-    <cfRule type="containsText" dxfId="52" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
+  <conditionalFormatting sqref="G16">
+    <cfRule type="containsText" dxfId="94" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="containsText" dxfId="93" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6600,7 +7730,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G15">
+  <conditionalFormatting sqref="G17:G18">
+    <cfRule type="containsText" dxfId="92" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17:G18">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6612,17 +7747,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G15">
-    <cfRule type="containsText" dxfId="51" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
-    <cfRule type="containsText" dxfId="50" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
+  <conditionalFormatting sqref="H17:H18">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6634,7 +7759,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16">
+  <conditionalFormatting sqref="H17:H18">
+    <cfRule type="containsText" dxfId="91" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="containsText" dxfId="26" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6646,17 +7781,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16">
-    <cfRule type="containsText" dxfId="49" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="containsText" dxfId="48" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
+  <conditionalFormatting sqref="H19">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6668,12 +7793,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
-    <cfRule type="containsText" dxfId="47" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="24" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6685,7 +7815,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H18">
+  <conditionalFormatting sqref="H20">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6697,9 +7827,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H18">
-    <cfRule type="containsText" dxfId="46" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6710,7 +7840,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -6743,13 +7873,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="32"/>
       <c r="B2" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>29</v>
@@ -7151,7 +8281,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="3" t="str">
-        <f t="shared" ref="I15:I18" si="1">IF(OR(AND(G15&gt;1,G15&lt;&gt;"-"),AND(H15&gt;1,H15&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I15:I20" si="1">IF(OR(AND(G15&gt;1,G15&lt;&gt;"-"),AND(H15&gt;1,H15&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -7228,19 +8358,79 @@
       <c r="D18" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="18">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3" t="str">
+      <c r="F19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -7255,6 +8445,261 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="H14:H15">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G15">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H10">
+    <cfRule type="containsText" dxfId="90" priority="47" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H10">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="89" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="containsText" dxfId="88" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11">
+    <cfRule type="containsText" dxfId="87" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="86" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G15">
+    <cfRule type="containsText" dxfId="85" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14:H15">
+    <cfRule type="containsText" dxfId="84" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="containsText" dxfId="83" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G7 G9:G10">
+    <cfRule type="containsText" dxfId="82" priority="49" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G7 G9:G10">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="containsText" dxfId="80" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="containsText" dxfId="79" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G16">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G16">
+    <cfRule type="containsText" dxfId="77" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="containsText" dxfId="76" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17:H18">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17">
+    <cfRule type="containsText" dxfId="10" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17:H18">
+    <cfRule type="containsText" dxfId="9" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7266,153 +8711,51 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12:G15">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H10">
-    <cfRule type="containsText" dxfId="45" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H10">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="44" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="containsText" dxfId="43" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
-    <cfRule type="containsText" dxfId="42" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="41" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12:G15">
-    <cfRule type="containsText" dxfId="40" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14:H15">
-    <cfRule type="containsText" dxfId="39" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
-    <cfRule type="containsText" dxfId="38" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G7 G9:G10">
-    <cfRule type="containsText" dxfId="37" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G7 G9:G10">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
-    <cfRule type="containsText" dxfId="36" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
+  <conditionalFormatting sqref="G18">
+    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7424,41 +8767,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="35" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="34" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H18">
+  <conditionalFormatting sqref="H20">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7470,43 +8779,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H18">
-    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G16">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G16">
-    <cfRule type="containsText" dxfId="32" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="containsText" dxfId="31" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7517,7 +8792,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -7550,13 +8825,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="32"/>
       <c r="B2" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>29</v>
@@ -7958,7 +9233,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="3" t="str">
-        <f t="shared" ref="I15:I18" si="1">IF(OR(AND(G15&gt;1,G15&lt;&gt;"-"),AND(H15&gt;1,H15&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I15:I20" si="1">IF(OR(AND(G15&gt;1,G15&lt;&gt;"-"),AND(H15&gt;1,H15&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -8035,19 +9310,79 @@
       <c r="D18" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="18">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3" t="str">
+      <c r="F19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8062,6 +9397,193 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G12:G15">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H10">
+    <cfRule type="containsText" dxfId="75" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H10">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="74" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="containsText" dxfId="73" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11">
+    <cfRule type="containsText" dxfId="72" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="71" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G15">
+    <cfRule type="containsText" dxfId="70" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="containsText" dxfId="69" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="containsText" dxfId="68" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G7 G9:G10">
+    <cfRule type="containsText" dxfId="67" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G7 G9:G10">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G16">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G16">
+    <cfRule type="containsText" dxfId="66" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="containsText" dxfId="65" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8073,43 +9595,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
+  <conditionalFormatting sqref="H12">
+    <cfRule type="containsText" dxfId="64" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8121,71 +9612,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H10">
-    <cfRule type="containsText" dxfId="30" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H10">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="29" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="containsText" dxfId="28" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
-    <cfRule type="containsText" dxfId="27" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="26" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12:G15">
-    <cfRule type="containsText" dxfId="25" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="24" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
-    <cfRule type="containsText" dxfId="23" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
+  <conditionalFormatting sqref="H14">
+    <cfRule type="containsText" dxfId="63" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8197,24 +9629,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G7 G9:G10">
-    <cfRule type="containsText" dxfId="22" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G7 G9:G10">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G16">
+  <conditionalFormatting sqref="H15">
+    <cfRule type="containsText" dxfId="62" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8226,7 +9646,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
+  <conditionalFormatting sqref="H17:H18">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8238,17 +9658,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G16">
-    <cfRule type="containsText" dxfId="21" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="containsText" dxfId="20" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
+  <conditionalFormatting sqref="G17">
+    <cfRule type="containsText" dxfId="61" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17:H18">
+    <cfRule type="containsText" dxfId="60" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8260,12 +9680,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="19" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
+  <conditionalFormatting sqref="G18">
+    <cfRule type="containsText" dxfId="22" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="containsText" dxfId="21" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8277,12 +9702,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
-    <cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
+  <conditionalFormatting sqref="H19">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8294,12 +9714,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
-    <cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="20" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="19" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8311,7 +9736,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H18">
+  <conditionalFormatting sqref="H20">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8323,14 +9748,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
-    <cfRule type="containsText" dxfId="16" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H18">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8341,7 +9761,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -8374,13 +9794,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="32"/>
       <c r="B2" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>29</v>
@@ -8842,7 +10262,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="3" t="str">
-        <f t="shared" ref="I17:I18" si="2">IF(OR(AND(G17&gt;1,G17&lt;&gt;"-"),AND(H17&gt;1,H17&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="I17:I20" si="2">IF(OR(AND(G17&gt;1,G17&lt;&gt;"-"),AND(H17&gt;1,H17&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -8872,6 +10292,66 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -8886,6 +10366,176 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G12:G16">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12:H16">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="59" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="containsText" dxfId="58" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11">
+    <cfRule type="containsText" dxfId="57" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="56" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G16">
+    <cfRule type="containsText" dxfId="55" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12:H16">
+    <cfRule type="containsText" dxfId="54" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="containsText" dxfId="53" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="containsText" dxfId="52" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4 G9:G10 G6:G7">
+    <cfRule type="containsText" dxfId="51" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G9:G10 G4 G6:G7">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H10">
+    <cfRule type="containsText" dxfId="50" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H10">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17:G18">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8897,43 +10547,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12:H16">
+  <conditionalFormatting sqref="H17:H18">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8945,7 +10559,22 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
+  <conditionalFormatting sqref="G17:G18">
+    <cfRule type="containsText" dxfId="49" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17:H18">
+    <cfRule type="containsText" dxfId="48" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8957,59 +10586,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="14" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H3">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11">
-    <cfRule type="containsText" dxfId="13" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11">
-    <cfRule type="containsText" dxfId="12" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="11" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12:G16">
-    <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12:H16">
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8">
-    <cfRule type="containsText" dxfId="8" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G5">
+  <conditionalFormatting sqref="H19">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9021,41 +10598,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4 G9:G10 G6:G7">
-    <cfRule type="containsText" dxfId="6" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G9:G10 G4 G6:G7">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H10">
-    <cfRule type="containsText" dxfId="5" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H10">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9067,7 +10620,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H18">
+  <conditionalFormatting sqref="H20">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9079,14 +10632,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H18">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H20))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
